--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SLIIT\3year1sem\ITPM\Test assign\test_automation\IT3040-Assignment1-Singlish-Transliteration-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC897DB-921A-44D6-9CC5-E584CAAA63AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CFF9A4-8C33-44A8-A4CA-A44006D5FEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,9 +67,6 @@
     <t>Neg_0003</t>
   </si>
   <si>
-    <t>dnma gedarata ynna.</t>
-  </si>
-  <si>
     <t>දැන්ම ගෙදරට යන්න.</t>
   </si>
   <si>
@@ -79,18 +76,12 @@
     <t>M</t>
   </si>
   <si>
-    <t>meka copy krla group akata danna.</t>
-  </si>
-  <si>
     <t>මේක copy කරලා group එකට දාන්න.</t>
   </si>
   <si>
     <t>Neg_0005</t>
   </si>
   <si>
-    <t>suba udasanak yaluwa!</t>
-  </si>
-  <si>
     <t>සුබ උදෑසනක් යාලුවා!</t>
   </si>
   <si>
@@ -100,9 +91,6 @@
     <t>Neg_0006</t>
   </si>
   <si>
-    <t>suba udeyk hamotama!</t>
-  </si>
-  <si>
     <t>සුබ උදෑසනක් හැමෝටම!</t>
   </si>
   <si>
@@ -112,9 +100,6 @@
     <t>Neg_0007</t>
   </si>
   <si>
-    <t>puluwannam mata call ekak denna.</t>
-  </si>
-  <si>
     <t>පුළුවන්නම් මට call එකක් දෙන්න.</t>
   </si>
   <si>
@@ -124,36 +109,24 @@
     <t>Neg_0008</t>
   </si>
   <si>
-    <t>karunakarala report eka ada ewanna.</t>
-  </si>
-  <si>
     <t>කරුණාකරලා report එක අද එවන්න.</t>
   </si>
   <si>
     <t>Neg_0009</t>
   </si>
   <si>
-    <t>hari mama ennam.</t>
-  </si>
-  <si>
     <t>හරි මම එන්නම්.</t>
   </si>
   <si>
     <t>Neg_0010</t>
   </si>
   <si>
-    <t>ow eka hari.</t>
-  </si>
-  <si>
     <t>ඔව් ඒක හරි.</t>
   </si>
   <si>
     <t>Neg_0011</t>
   </si>
   <si>
-    <t>tikak tikak theruna.</t>
-  </si>
-  <si>
     <t>ටිකක් ටිකක් තේරුණා.</t>
   </si>
   <si>
@@ -163,36 +136,24 @@
     <t>Neg_0012</t>
   </si>
   <si>
-    <t>epa epa dan katha karanna epa.</t>
-  </si>
-  <si>
     <t>එපා එපා දැන් කතා කරන්න එපා.</t>
   </si>
   <si>
     <t>Neg_0013</t>
   </si>
   <si>
-    <t>ei mehema une?</t>
-  </si>
-  <si>
     <t>ඇයි මෙහෙම උනේ?</t>
   </si>
   <si>
     <t>Neg_0014</t>
   </si>
   <si>
-    <t>ane... mata aka amathaka una!</t>
-  </si>
-  <si>
     <t>අනේ... මට ඒක අමතක උනා!</t>
   </si>
   <si>
     <t>Neg_0015</t>
   </si>
   <si>
-    <t>mn oyta heta msg ekak dannm.</t>
-  </si>
-  <si>
     <t>මං ඔයාට හෙට msg එකක් දාන්නම්.</t>
   </si>
   <si>
@@ -202,90 +163,60 @@
     <t>Neg_0016</t>
   </si>
   <si>
-    <t>oyge gedra kauda inne?</t>
-  </si>
-  <si>
     <t>ඔයාගේ ගෙදර කවුද ඉන්නේ?</t>
   </si>
   <si>
     <t>Neg_0017</t>
   </si>
   <si>
-    <t>mama ada lunch eka gedarin genawa.</t>
-  </si>
-  <si>
     <t>මම අද lunch එක ගෙදරින් ගෙනාවා.</t>
   </si>
   <si>
     <t>Neg_0018</t>
   </si>
   <si>
-    <t>ape sir assignment eka check kala.</t>
-  </si>
-  <si>
     <t>අපේ sir assignment එක check කළා.</t>
   </si>
   <si>
     <t>Neg_0019</t>
   </si>
   <si>
-    <t>mama dan ready to go inne.</t>
-  </si>
-  <si>
     <t>මම දැන් ready to go ඉන්නේ.</t>
   </si>
   <si>
     <t>Neg_0020</t>
   </si>
   <si>
-    <t>oya please wait karanna mama enakan.</t>
-  </si>
-  <si>
     <t>ඔයා please wait කරන්න මම එනකන්.</t>
   </si>
   <si>
     <t>Neg_0021</t>
   </si>
   <si>
-    <t>mage email eka update karanna.</t>
-  </si>
-  <si>
     <t>මගේ email එක update කරන්න.</t>
   </si>
   <si>
     <t>Neg_0022</t>
   </si>
   <si>
-    <t>password eka reset karanna puluwanda?</t>
-  </si>
-  <si>
     <t>password එක reset කරන්න පුළුවන්ද?</t>
   </si>
   <si>
     <t>Neg_0023</t>
   </si>
   <si>
-    <t>Teams meeting aka heta thiyenawa.</t>
-  </si>
-  <si>
     <t>Teams meeting එක හෙට තියෙනවා.</t>
   </si>
   <si>
     <t>Neg_0024</t>
   </si>
   <si>
-    <t>Telegram group akata msg ekak danna.</t>
-  </si>
-  <si>
     <t>Telegram group එකට msg එකක් දාන්න.</t>
   </si>
   <si>
     <t>Neg_0025</t>
   </si>
   <si>
-    <t>CV eka PDF widihata upload karanna.</t>
-  </si>
-  <si>
     <t>CV එක PDF විදිහට upload කරන්න.</t>
   </si>
   <si>
@@ -295,54 +226,36 @@
     <t>Neg_0026</t>
   </si>
   <si>
-    <t>ID card eka scan karala ewanna.</t>
-  </si>
-  <si>
     <t>ID card එක scan කරලා එවන්න.</t>
   </si>
   <si>
     <t>Neg_0027</t>
   </si>
   <si>
-    <t>heta practical ekata enna.</t>
-  </si>
-  <si>
     <t>හෙට practical එකට එන්න.</t>
   </si>
   <si>
     <t>Neg_0028</t>
   </si>
   <si>
-    <t>lab report eka submit karada?</t>
-  </si>
-  <si>
     <t>lab report එක submit කරාද?</t>
   </si>
   <si>
     <t>Neg_0029</t>
   </si>
   <si>
-    <t>api heta Kandy walata yanawa.</t>
-  </si>
-  <si>
     <t>අපි හෙට Kandy වලට යනවා.</t>
   </si>
   <si>
     <t>Neg_0030</t>
   </si>
   <si>
-    <t>mama Colombo Fort eken bus ekata nagga.</t>
-  </si>
-  <si>
     <t>මම Colombo Fort එකෙන් bus එකට නැග්ගා.</t>
   </si>
   <si>
     <t>Neg_0031</t>
   </si>
   <si>
-    <t>Kasun ada exam ekata awe na.</t>
-  </si>
-  <si>
     <t>Kasun අද exam එකට ආවේ නෑ.</t>
   </si>
   <si>
@@ -352,9 +265,6 @@
     <t>Neg_0032</t>
   </si>
   <si>
-    <t>Nethmi presentation eka lassanata kala.</t>
-  </si>
-  <si>
     <t>Nethmi presentation එක ලස්සනට කළා.</t>
   </si>
   <si>
@@ -364,36 +274,24 @@
     <t>Neg_0033</t>
   </si>
   <si>
-    <t>mata 2nd attempt ekata register wenna one.</t>
-  </si>
-  <si>
     <t>මට 2nd attempt එකට register වෙන්න ඕනේ.</t>
   </si>
   <si>
     <t>Neg_0034</t>
   </si>
   <si>
-    <t>lamai 25k class akata awa.</t>
-  </si>
-  <si>
     <t>ළමයි 25ක් class එකට ආවා.</t>
   </si>
   <si>
     <t>Neg_0035</t>
   </si>
   <si>
-    <t>mata Rs. 1500k transfer karanna.</t>
-  </si>
-  <si>
     <t>මට Rs. 1500ක් transfer කරන්න.</t>
   </si>
   <si>
     <t>Neg_0036</t>
   </si>
   <si>
-    <t>dollar 20k gewanna una.</t>
-  </si>
-  <si>
     <t>dollar 20ක් ගෙවන්න උනා.</t>
   </si>
   <si>
@@ -403,18 +301,12 @@
     <t>Neg_0037</t>
   </si>
   <si>
-    <t>class eka 8.30pm patan gannawa.</t>
-  </si>
-  <si>
     <t>class එක 8.30pm පටන් ගන්නවා.</t>
   </si>
   <si>
     <t>Neg_0038</t>
   </si>
   <si>
-    <t>mata 10:15AM walata mathak karanna.</t>
-  </si>
-  <si>
     <t>මට 10:15AM වෙලාවට මතක් කරන්න.</t>
   </si>
   <si>
@@ -424,45 +316,30 @@
     <t>Neg_0039</t>
   </si>
   <si>
-    <t>exam eka 2026-05-12 wenida thiyenawa.</t>
-  </si>
-  <si>
     <t>exam එක 2026-05-12 වෙනිදා තියෙනවා.</t>
   </si>
   <si>
     <t>Neg_0040</t>
   </si>
   <si>
-    <t>assignment eka March 3ta kalin denna.</t>
-  </si>
-  <si>
     <t>assignment එක March 3ට කලින් දෙන්න.</t>
   </si>
   <si>
     <t>Neg_0041</t>
   </si>
   <si>
-    <t>mata 500g seeni genna.</t>
-  </si>
-  <si>
     <t>මට 500g සීනි ගේන්න.</t>
   </si>
   <si>
     <t>Neg_0042</t>
   </si>
   <si>
-    <t>bike eka 5km withara giya.</t>
-  </si>
-  <si>
     <t>bike එක 5km විතර ගියා.</t>
   </si>
   <si>
     <t>Neg_0043</t>
   </si>
   <si>
-    <t>patta machan oya wede goda dagaththa.</t>
-  </si>
-  <si>
     <t>පට්ට මචං ඔයා වැඩේ ගොඩ දාගත්තා.</t>
   </si>
   <si>
@@ -472,18 +349,12 @@
     <t>Neg_0044</t>
   </si>
   <si>
-    <t>ado mata podi help ekak one.</t>
-  </si>
-  <si>
     <t>අඩෝ මට පොඩි help එකක් ඕනේ.</t>
   </si>
   <si>
     <t>Neg_0045</t>
   </si>
   <si>
-    <t>me link eka open karanna: https://sliit.lk</t>
-  </si>
-  <si>
     <t>මේ link එක open කරන්න: https://sliit.lk</t>
   </si>
   <si>
@@ -493,9 +364,6 @@
     <t>Neg_0046</t>
   </si>
   <si>
-    <t>mata email ekak danna: raki2026@gmail.com</t>
-  </si>
-  <si>
     <t>මට email එකක් දාන්න: raki2026@gmail.com</t>
   </si>
   <si>
@@ -505,18 +373,12 @@
     <t>Neg_0047</t>
   </si>
   <si>
-    <t>mata dan hina yanawa 😂</t>
-  </si>
-  <si>
     <t>මට දැන් හිනා යනවා 😂</t>
   </si>
   <si>
     <t>Neg_0048</t>
   </si>
   <si>
-    <t>oya wede hodata kala ❤️</t>
-  </si>
-  <si>
     <t>ඔයා වැඩේ හොඳට කළා ❤️</t>
   </si>
   <si>
@@ -554,6 +416,144 @@
   </si>
   <si>
     <t>ada class ek tiyenwada?</t>
+  </si>
+  <si>
+    <t>dnm gedrta ynn.</t>
+  </si>
+  <si>
+    <t>mek copy krl group akt dnna.</t>
+  </si>
+  <si>
+    <t>sub udasanak yaluwa!</t>
+  </si>
+  <si>
+    <t>sub udeyk hamotama!</t>
+  </si>
+  <si>
+    <t>puluwnnam mt call ekk denna.</t>
+  </si>
+  <si>
+    <t>karunkarala report ek ada ewnna.</t>
+  </si>
+  <si>
+    <t>hri man ennam.</t>
+  </si>
+  <si>
+    <t>ow ek hari.</t>
+  </si>
+  <si>
+    <t>tikk tikk teruna.</t>
+  </si>
+  <si>
+    <t>ep ep dn kata karnna epa.</t>
+  </si>
+  <si>
+    <t>aye mehma une?</t>
+  </si>
+  <si>
+    <t>ane... mt ak amthka una!</t>
+  </si>
+  <si>
+    <t>mn oyt heta msg ekk dnnm.</t>
+  </si>
+  <si>
+    <t>oyge gedr kuda inne?</t>
+  </si>
+  <si>
+    <t>man ada lunch eka gedarin genawa.</t>
+  </si>
+  <si>
+    <t>ape sir assignment ek check kl.</t>
+  </si>
+  <si>
+    <t>man dn ready to go inne.</t>
+  </si>
+  <si>
+    <t>oya please wait karann mma enkn.</t>
+  </si>
+  <si>
+    <t>mge email ek update karnn.</t>
+  </si>
+  <si>
+    <t>password ek reset krnna puluwanda?</t>
+  </si>
+  <si>
+    <t>Teams meeting ak heta thiyenawa.</t>
+  </si>
+  <si>
+    <t>Telegram group akt msg ekk danna.</t>
+  </si>
+  <si>
+    <t>CV ek PDF widihta upload karnna.</t>
+  </si>
+  <si>
+    <t>ID card ek scan karla ewnna.</t>
+  </si>
+  <si>
+    <t>het practical ekta enna.</t>
+  </si>
+  <si>
+    <t>lab report ek submit karda?</t>
+  </si>
+  <si>
+    <t>api heta Kandy wlt ynawa.</t>
+  </si>
+  <si>
+    <t>mn Colombo Fort eken bus ekata nagga.</t>
+  </si>
+  <si>
+    <t>Kasun ada exam ekt awe na.</t>
+  </si>
+  <si>
+    <t>Nethmi presentation ek lssnt kala.</t>
+  </si>
+  <si>
+    <t>mt 2nd attempt ekt register wenna one.</t>
+  </si>
+  <si>
+    <t>lamai 25k class ekt awa.</t>
+  </si>
+  <si>
+    <t>mt Rs. 1500k transfer krnna.</t>
+  </si>
+  <si>
+    <t>Dollar 20k gewnna una.</t>
+  </si>
+  <si>
+    <t>class ek 8.30pm ptn gnnawa.</t>
+  </si>
+  <si>
+    <t>mt 10:15AM wlt mtk krnna.</t>
+  </si>
+  <si>
+    <t>exam ek 2026-05-12 wenida thiyenwa.</t>
+  </si>
+  <si>
+    <t>assignment ek March 3t klin denna.</t>
+  </si>
+  <si>
+    <t>mt 500g sini genna.</t>
+  </si>
+  <si>
+    <t>bike ek 5km witra giya.</t>
+  </si>
+  <si>
+    <t>ptt machan oya wede goda dgththa.</t>
+  </si>
+  <si>
+    <t>ado mt podi help ekk one.</t>
+  </si>
+  <si>
+    <t>me link ek open krnna: https://sliit.lk</t>
+  </si>
+  <si>
+    <t>mt email ekk danna: raki2026@gmail.com</t>
+  </si>
+  <si>
+    <t>mt dn hina ynwa 😂</t>
+  </si>
+  <si>
+    <t>oya wede hodt kala ❤️</t>
   </si>
 </sst>
 </file>
@@ -700,13 +700,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -1032,7 +1032,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -1040,7 +1040,7 @@
       <c r="E2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1076,15 +1076,15 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1120,15 +1120,15 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1158,21 +1158,21 @@
     </row>
     <row r="14" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="8" t="s">
+      <c r="E14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1202,21 +1202,21 @@
     </row>
     <row r="18" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>22</v>
+        <v>134</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1246,21 +1246,21 @@
     </row>
     <row r="22" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1290,21 +1290,21 @@
     </row>
     <row r="26" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1334,21 +1334,21 @@
     </row>
     <row r="30" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1378,21 +1378,21 @@
     </row>
     <row r="34" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1422,21 +1422,21 @@
     </row>
     <row r="38" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F38" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1466,21 +1466,21 @@
     </row>
     <row r="42" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F42" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1510,21 +1510,21 @@
     </row>
     <row r="46" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1554,21 +1554,21 @@
     </row>
     <row r="50" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F50" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1598,21 +1598,21 @@
     </row>
     <row r="54" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F54" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1642,21 +1642,21 @@
     </row>
     <row r="58" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F58" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1686,21 +1686,21 @@
     </row>
     <row r="62" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F62" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1730,21 +1730,21 @@
     </row>
     <row r="66" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F66" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F66" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1774,21 +1774,21 @@
     </row>
     <row r="70" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F70" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F70" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1818,21 +1818,21 @@
     </row>
     <row r="74" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F74" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1862,21 +1862,21 @@
     </row>
     <row r="78" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F78" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F78" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
     </row>
     <row r="82" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F82" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1950,21 +1950,21 @@
     </row>
     <row r="86" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F86" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F86" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1994,21 +1994,21 @@
     </row>
     <row r="90" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F90" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2038,21 +2038,21 @@
     </row>
     <row r="94" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F94" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F94" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2082,21 +2082,21 @@
     </row>
     <row r="98" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F98" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F98" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2126,21 +2126,21 @@
     </row>
     <row r="102" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F102" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F102" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2170,21 +2170,21 @@
     </row>
     <row r="106" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F106" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2214,21 +2214,21 @@
     </row>
     <row r="110" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F110" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F110" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2258,21 +2258,21 @@
     </row>
     <row r="114" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F114" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F114" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2302,21 +2302,21 @@
     </row>
     <row r="118" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F118" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F118" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2346,21 +2346,21 @@
     </row>
     <row r="122" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F122" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F122" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2390,21 +2390,21 @@
     </row>
     <row r="126" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F126" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F126" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2434,21 +2434,21 @@
     </row>
     <row r="130" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F130" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F130" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2478,21 +2478,21 @@
     </row>
     <row r="134" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F134" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F134" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2522,21 +2522,21 @@
     </row>
     <row r="138" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E138" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F138" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F138" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2566,21 +2566,21 @@
     </row>
     <row r="142" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F142" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F142" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2610,21 +2610,21 @@
     </row>
     <row r="146" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F146" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F146" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2654,21 +2654,21 @@
     </row>
     <row r="150" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F150" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F150" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2698,21 +2698,21 @@
     </row>
     <row r="154" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E154" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F154" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F154" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2742,21 +2742,21 @@
     </row>
     <row r="158" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F158" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F158" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2786,21 +2786,21 @@
     </row>
     <row r="162" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F162" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F162" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2830,21 +2830,21 @@
     </row>
     <row r="166" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E166" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F166" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F166" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2874,21 +2874,21 @@
     </row>
     <row r="170" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F170" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F170" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2918,21 +2918,21 @@
     </row>
     <row r="174" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F174" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F174" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2962,21 +2962,21 @@
     </row>
     <row r="178" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="F178" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F178" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3006,21 +3006,21 @@
     </row>
     <row r="182" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F182" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3050,21 +3050,21 @@
     </row>
     <row r="186" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E186" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F186" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F186" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3094,21 +3094,21 @@
     </row>
     <row r="190" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="F190" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F190" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3138,21 +3138,21 @@
     </row>
     <row r="194" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E194" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F194" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F194" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3182,21 +3182,21 @@
     </row>
     <row r="198" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E198" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F198" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F198" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3226,6 +3226,282 @@
     </row>
   </sheetData>
   <mergeCells count="300">
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="E102:E105"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="D198:D201"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="F198:F201"/>
+    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="D174:D177"/>
+    <mergeCell ref="F174:F177"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="D126:D129"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="F126:F129"/>
+    <mergeCell ref="D166:D169"/>
+    <mergeCell ref="E94:E97"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="F150:F153"/>
+    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="E154:E157"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="E130:E133"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="E186:E189"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="E174:E177"/>
+    <mergeCell ref="D142:D145"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="F146:F149"/>
+    <mergeCell ref="E150:E153"/>
+    <mergeCell ref="D178:D181"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="F178:F181"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="D170:D173"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="C134:C137"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E170:E173"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C138:C141"/>
+    <mergeCell ref="C178:C181"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E178:E181"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="C166:C169"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="D154:D157"/>
+    <mergeCell ref="C162:C165"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="D182:D185"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="F182:F185"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="E146:E149"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="F166:F169"/>
+    <mergeCell ref="E198:E201"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="F162:F165"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="F154:F157"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="D186:D189"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="F138:F141"/>
+    <mergeCell ref="C142:C145"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="E118:E121"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="E166:E169"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="F158:F161"/>
+    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="E162:E165"/>
+    <mergeCell ref="D130:D133"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="F130:F133"/>
+    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="E134:E137"/>
+    <mergeCell ref="D138:D141"/>
+    <mergeCell ref="F54:F57"/>
+    <mergeCell ref="C158:C161"/>
+    <mergeCell ref="F190:F193"/>
+    <mergeCell ref="E190:E193"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="F134:F137"/>
+    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="D58:D61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="F58:F61"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="C186:C189"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="E142:E145"/>
+    <mergeCell ref="E194:E197"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="C170:C173"/>
+    <mergeCell ref="F78:F81"/>
+    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="C174:C177"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="D190:D193"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="F86:F89"/>
+    <mergeCell ref="F142:F145"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="B182:B185"/>
+    <mergeCell ref="D134:D137"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="A98:A101"/>
@@ -3250,282 +3526,6 @@
     <mergeCell ref="B114:B117"/>
     <mergeCell ref="D114:D117"/>
     <mergeCell ref="B154:B157"/>
-    <mergeCell ref="C174:C177"/>
-    <mergeCell ref="F170:F173"/>
-    <mergeCell ref="B138:B141"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="D190:D193"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="A138:A141"/>
-    <mergeCell ref="E82:E85"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="F86:F89"/>
-    <mergeCell ref="F142:F145"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="E98:E101"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="B182:B185"/>
-    <mergeCell ref="D134:D137"/>
-    <mergeCell ref="F134:F137"/>
-    <mergeCell ref="E62:E65"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="C194:C197"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="D58:D61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="F58:F61"/>
-    <mergeCell ref="A122:A125"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="A186:A189"/>
-    <mergeCell ref="C186:C189"/>
-    <mergeCell ref="D94:D97"/>
-    <mergeCell ref="E142:E145"/>
-    <mergeCell ref="E194:E197"/>
-    <mergeCell ref="B150:B153"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="C170:C173"/>
-    <mergeCell ref="F78:F81"/>
-    <mergeCell ref="F118:F121"/>
-    <mergeCell ref="F158:F161"/>
-    <mergeCell ref="B190:B193"/>
-    <mergeCell ref="D194:D197"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="E86:E89"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="E162:E165"/>
-    <mergeCell ref="D130:D133"/>
-    <mergeCell ref="A134:A137"/>
-    <mergeCell ref="B162:B165"/>
-    <mergeCell ref="F130:F133"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="E134:E137"/>
-    <mergeCell ref="D138:D141"/>
-    <mergeCell ref="F54:F57"/>
-    <mergeCell ref="C158:C161"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="F154:F157"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="D186:D189"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="F138:F141"/>
-    <mergeCell ref="C142:C145"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="E118:E121"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="D106:D109"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="F66:F69"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="E166:E169"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B198:B201"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="B174:B177"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="D182:D185"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="F182:F185"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="E106:E109"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="E146:E149"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="F166:F169"/>
-    <mergeCell ref="E198:E201"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="F162:F165"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="F190:F193"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C138:C141"/>
-    <mergeCell ref="C178:C181"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="E178:E181"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="F62:F65"/>
-    <mergeCell ref="E126:E129"/>
-    <mergeCell ref="C166:C169"/>
-    <mergeCell ref="C126:C129"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="E58:E61"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="E190:E193"/>
-    <mergeCell ref="D158:D161"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="D154:D157"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="B170:B173"/>
-    <mergeCell ref="E78:E81"/>
-    <mergeCell ref="A174:A177"/>
-    <mergeCell ref="D170:D173"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="C134:C137"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="A154:A157"/>
-    <mergeCell ref="E30:E33"/>
-    <mergeCell ref="E170:E173"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F102:F105"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="F146:F149"/>
-    <mergeCell ref="E150:E153"/>
-    <mergeCell ref="D178:D181"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="F178:F181"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="F74:F77"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="E186:E189"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="B186:B189"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D102:D105"/>
-    <mergeCell ref="B142:B145"/>
-    <mergeCell ref="E174:E177"/>
-    <mergeCell ref="D142:D145"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A150:A153"/>
-    <mergeCell ref="E26:E29"/>
-    <mergeCell ref="D98:D101"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="E66:E69"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="D198:D201"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="F198:F201"/>
-    <mergeCell ref="C146:C149"/>
-    <mergeCell ref="D174:D177"/>
-    <mergeCell ref="F174:F177"/>
-    <mergeCell ref="A178:A181"/>
-    <mergeCell ref="D126:D129"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="F126:F129"/>
-    <mergeCell ref="D166:D169"/>
-    <mergeCell ref="E94:E97"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="F150:F153"/>
-    <mergeCell ref="E158:E161"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="E154:E157"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="E130:E133"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="C162:C165"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E74:E77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="F82:F85"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="C154:C157"/>
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="E102:E105"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="A162:A165"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="E18:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -700,13 +700,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -1040,7 +1040,7 @@
       <c r="E2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1081,10 +1081,10 @@
       <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1125,10 +1125,10 @@
       <c r="D10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1169,10 +1169,10 @@
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1213,10 +1213,10 @@
       <c r="D18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1257,10 +1257,10 @@
       <c r="D22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1301,10 +1301,10 @@
       <c r="D26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1345,10 +1345,10 @@
       <c r="D30" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1389,10 +1389,10 @@
       <c r="D34" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1433,10 +1433,10 @@
       <c r="D38" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1477,10 +1477,10 @@
       <c r="D42" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1521,10 +1521,10 @@
       <c r="D46" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1565,10 +1565,10 @@
       <c r="D50" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1609,10 +1609,10 @@
       <c r="D54" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1653,10 +1653,10 @@
       <c r="D58" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1697,10 +1697,10 @@
       <c r="D62" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1741,10 +1741,10 @@
       <c r="D66" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1785,10 +1785,10 @@
       <c r="D70" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1829,10 +1829,10 @@
       <c r="D74" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
       <c r="D78" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="F78" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1917,10 +1917,10 @@
       <c r="D82" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="F82" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1961,10 +1961,10 @@
       <c r="D86" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E86" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="F86" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2005,10 +2005,10 @@
       <c r="D90" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F90" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2049,10 +2049,10 @@
       <c r="D94" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E94" s="8" t="s">
+      <c r="E94" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="F94" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2093,10 +2093,10 @@
       <c r="D98" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E98" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="F98" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2137,10 +2137,10 @@
       <c r="D102" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E102" s="8" t="s">
+      <c r="E102" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F102" s="5" t="s">
+      <c r="F102" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2181,10 +2181,10 @@
       <c r="D106" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E106" s="8" t="s">
+      <c r="E106" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F106" s="5" t="s">
+      <c r="F106" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2225,10 +2225,10 @@
       <c r="D110" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E110" s="8" t="s">
+      <c r="E110" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="F110" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2269,10 +2269,10 @@
       <c r="D114" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E114" s="8" t="s">
+      <c r="E114" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F114" s="5" t="s">
+      <c r="F114" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2313,10 +2313,10 @@
       <c r="D118" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E118" s="8" t="s">
+      <c r="E118" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="F118" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2357,10 +2357,10 @@
       <c r="D122" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E122" s="8" t="s">
+      <c r="E122" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F122" s="5" t="s">
+      <c r="F122" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2401,10 +2401,10 @@
       <c r="D126" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E126" s="8" t="s">
+      <c r="E126" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F126" s="5" t="s">
+      <c r="F126" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2445,10 +2445,10 @@
       <c r="D130" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E130" s="8" t="s">
+      <c r="E130" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="F130" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2489,10 +2489,10 @@
       <c r="D134" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E134" s="8" t="s">
+      <c r="E134" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F134" s="5" t="s">
+      <c r="F134" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2533,10 +2533,10 @@
       <c r="D138" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E138" s="8" t="s">
+      <c r="E138" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F138" s="5" t="s">
+      <c r="F138" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2577,10 +2577,10 @@
       <c r="D142" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E142" s="8" t="s">
+      <c r="E142" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F142" s="5" t="s">
+      <c r="F142" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2621,10 +2621,10 @@
       <c r="D146" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E146" s="8" t="s">
+      <c r="E146" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="F146" s="5" t="s">
+      <c r="F146" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2665,10 +2665,10 @@
       <c r="D150" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E150" s="8" t="s">
+      <c r="E150" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F150" s="5" t="s">
+      <c r="F150" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2709,10 +2709,10 @@
       <c r="D154" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E154" s="8" t="s">
+      <c r="E154" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F154" s="5" t="s">
+      <c r="F154" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2753,10 +2753,10 @@
       <c r="D158" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E158" s="8" t="s">
+      <c r="E158" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F158" s="5" t="s">
+      <c r="F158" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2797,10 +2797,10 @@
       <c r="D162" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E162" s="8" t="s">
+      <c r="E162" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F162" s="5" t="s">
+      <c r="F162" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2841,10 +2841,10 @@
       <c r="D166" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E166" s="8" t="s">
+      <c r="E166" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F166" s="5" t="s">
+      <c r="F166" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2885,10 +2885,10 @@
       <c r="D170" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E170" s="8" t="s">
+      <c r="E170" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F170" s="5" t="s">
+      <c r="F170" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2929,10 +2929,10 @@
       <c r="D174" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E174" s="8" t="s">
+      <c r="E174" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F174" s="5" t="s">
+      <c r="F174" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2973,10 +2973,10 @@
       <c r="D178" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E178" s="8" t="s">
+      <c r="E178" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F178" s="5" t="s">
+      <c r="F178" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3017,10 +3017,10 @@
       <c r="D182" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E182" s="8" t="s">
+      <c r="E182" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F182" s="5" t="s">
+      <c r="F182" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3061,10 +3061,10 @@
       <c r="D186" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E186" s="8" t="s">
+      <c r="E186" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F186" s="5" t="s">
+      <c r="F186" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3105,10 +3105,10 @@
       <c r="D190" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E190" s="8" t="s">
+      <c r="E190" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F190" s="5" t="s">
+      <c r="F190" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3149,10 +3149,10 @@
       <c r="D194" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E194" s="8" t="s">
+      <c r="E194" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F194" s="5" t="s">
+      <c r="F194" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3193,10 +3193,10 @@
       <c r="D198" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E198" s="8" t="s">
+      <c r="E198" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F198" s="5" t="s">
+      <c r="F198" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3226,42 +3226,244 @@
     </row>
   </sheetData>
   <mergeCells count="300">
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="C154:C157"/>
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="E102:E105"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="A162:A165"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="F82:F85"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E74:E77"/>
-    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="F194:F197"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="C198:C201"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="D162:D165"/>
+    <mergeCell ref="C130:C133"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="C182:C185"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="E182:E185"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="F106:F109"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="C150:C153"/>
+    <mergeCell ref="F186:F189"/>
+    <mergeCell ref="C190:C193"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="D190:D193"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="F86:F89"/>
+    <mergeCell ref="F142:F145"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="B182:B185"/>
+    <mergeCell ref="D134:D137"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="D58:D61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="F58:F61"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="C186:C189"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="E142:E145"/>
+    <mergeCell ref="E194:E197"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="C170:C173"/>
+    <mergeCell ref="F78:F81"/>
+    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="C174:C177"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="E162:E165"/>
+    <mergeCell ref="D130:D133"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="F130:F133"/>
+    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="E134:E137"/>
+    <mergeCell ref="D138:D141"/>
+    <mergeCell ref="F54:F57"/>
+    <mergeCell ref="C158:C161"/>
+    <mergeCell ref="F190:F193"/>
+    <mergeCell ref="E190:E193"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="F134:F137"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="F154:F157"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="D186:D189"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="F138:F141"/>
+    <mergeCell ref="C142:C145"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="E118:E121"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="E166:E169"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="D182:D185"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="F182:F185"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="E146:E149"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="F166:F169"/>
+    <mergeCell ref="E198:E201"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="F162:F165"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="D154:D157"/>
+    <mergeCell ref="C162:C165"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="F158:F161"/>
+    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="C178:C181"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E178:E181"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="C166:C169"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="D170:D173"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="C134:C137"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E170:E173"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="F146:F149"/>
+    <mergeCell ref="E150:E153"/>
+    <mergeCell ref="D178:D181"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="F178:F181"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="E186:E189"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="E174:E177"/>
+    <mergeCell ref="D142:D145"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="E66:E69"/>
     <mergeCell ref="D198:D201"/>
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A146:A149"/>
@@ -3286,246 +3488,44 @@
     <mergeCell ref="E110:E113"/>
     <mergeCell ref="E130:E133"/>
     <mergeCell ref="B134:B137"/>
-    <mergeCell ref="E186:E189"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="B186:B189"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D102:D105"/>
-    <mergeCell ref="B142:B145"/>
-    <mergeCell ref="E174:E177"/>
-    <mergeCell ref="D142:D145"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A150:A153"/>
-    <mergeCell ref="E26:E29"/>
-    <mergeCell ref="D98:D101"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="E66:E69"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="F146:F149"/>
-    <mergeCell ref="E150:E153"/>
-    <mergeCell ref="D178:D181"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="F178:F181"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="F74:F77"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="B170:B173"/>
-    <mergeCell ref="E78:E81"/>
-    <mergeCell ref="A174:A177"/>
-    <mergeCell ref="D170:D173"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="C134:C137"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="A154:A157"/>
-    <mergeCell ref="E30:E33"/>
-    <mergeCell ref="E170:E173"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F102:F105"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="E102:E105"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="C138:C141"/>
-    <mergeCell ref="C178:C181"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="E178:E181"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="F62:F65"/>
-    <mergeCell ref="E126:E129"/>
-    <mergeCell ref="C166:C169"/>
-    <mergeCell ref="C126:C129"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="E58:E61"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="D158:D161"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="D154:D157"/>
-    <mergeCell ref="C162:C165"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="B198:B201"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="B174:B177"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="D182:D185"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="F182:F185"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="E106:E109"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="E146:E149"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="F166:F169"/>
-    <mergeCell ref="E198:E201"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="F162:F165"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="F154:F157"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="D186:D189"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="F138:F141"/>
-    <mergeCell ref="C142:C145"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="E118:E121"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="D106:D109"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="F66:F69"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="E166:E169"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="F158:F161"/>
-    <mergeCell ref="B190:B193"/>
-    <mergeCell ref="D194:D197"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="E86:E89"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="E162:E165"/>
-    <mergeCell ref="D130:D133"/>
-    <mergeCell ref="A134:A137"/>
-    <mergeCell ref="B162:B165"/>
-    <mergeCell ref="F130:F133"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="E134:E137"/>
-    <mergeCell ref="D138:D141"/>
-    <mergeCell ref="F54:F57"/>
-    <mergeCell ref="C158:C161"/>
-    <mergeCell ref="F190:F193"/>
-    <mergeCell ref="E190:E193"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="F134:F137"/>
-    <mergeCell ref="E62:E65"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="C194:C197"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="D58:D61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="F58:F61"/>
-    <mergeCell ref="A122:A125"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="A186:A189"/>
-    <mergeCell ref="C186:C189"/>
-    <mergeCell ref="D94:D97"/>
-    <mergeCell ref="E142:E145"/>
-    <mergeCell ref="E194:E197"/>
-    <mergeCell ref="B150:B153"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="C170:C173"/>
-    <mergeCell ref="F78:F81"/>
-    <mergeCell ref="F118:F121"/>
-    <mergeCell ref="C174:C177"/>
-    <mergeCell ref="F170:F173"/>
-    <mergeCell ref="B138:B141"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="D190:D193"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="A138:A141"/>
-    <mergeCell ref="E82:E85"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="F86:F89"/>
-    <mergeCell ref="F142:F145"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="E98:E101"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="B182:B185"/>
-    <mergeCell ref="D134:D137"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="F194:F197"/>
-    <mergeCell ref="A198:A201"/>
-    <mergeCell ref="C198:C201"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="D162:D165"/>
-    <mergeCell ref="C130:C133"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="C182:C185"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="E182:E185"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="F106:F109"/>
-    <mergeCell ref="A190:A193"/>
-    <mergeCell ref="C150:C153"/>
-    <mergeCell ref="F186:F189"/>
-    <mergeCell ref="C190:C193"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="B154:B157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SLIIT\3year1sem\ITPM\Test assign\test_automation\IT3040-Assignment1-Singlish-Transliteration-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CFF9A4-8C33-44A8-A4CA-A44006D5FEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDBAAD27-7A9D-4FE8-8839-21D9E3C7795C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="199">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -49,57 +49,75 @@
     <t>ඔයාගේ නම මොකක්ද?</t>
   </si>
   <si>
-    <t>ඔයාගෙ නම මොකක්ද?</t>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Neg_0002</t>
+  </si>
+  <si>
+    <t>අද class එක තියෙනවද?</t>
+  </si>
+  <si>
+    <t>Neg_0003</t>
+  </si>
+  <si>
+    <t>dnm gedrta ynn.</t>
+  </si>
+  <si>
+    <t>දැන්ම ගෙදරට යන්න.</t>
+  </si>
+  <si>
+    <t>දැන් ගෙදරට යන්න.</t>
   </si>
   <si>
     <t>FAIL</t>
   </si>
   <si>
-    <t>Neg_0002</t>
-  </si>
-  <si>
-    <t>අද class එක තියෙනවද?</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>Neg_0003</t>
-  </si>
-  <si>
-    <t>දැන්ම ගෙදරට යන්න.</t>
-  </si>
-  <si>
     <t>Neg_0004</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
+    <t>mek copy krl group akt dnna.</t>
+  </si>
+  <si>
     <t>මේක copy කරලා group එකට දාන්න.</t>
   </si>
   <si>
+    <t>මේක කොපි කරලා group ආකෘත දාන්න.</t>
+  </si>
+  <si>
     <t>Neg_0005</t>
   </si>
   <si>
+    <t>sub udasanak yaluwa!</t>
+  </si>
+  <si>
     <t>සුබ උදෑසනක් යාලුවා!</t>
   </si>
   <si>
-    <t>සුබ උදසනක්‍යාලුවා!</t>
+    <t>සුබ් උදසනක්‍යාලුවා!</t>
   </si>
   <si>
     <t>Neg_0006</t>
   </si>
   <si>
+    <t>sub udeyk hamotama!</t>
+  </si>
+  <si>
     <t>සුබ උදෑසනක් හැමෝටම!</t>
   </si>
   <si>
-    <t>සුබ උදේයක් හැමෝටම!</t>
+    <t>සබ් උදේයක් හැමෝටම!</t>
   </si>
   <si>
     <t>Neg_0007</t>
   </si>
   <si>
+    <t>puluwnnam mt call ekk denna.</t>
+  </si>
+  <si>
     <t>පුළුවන්නම් මට call එකක් දෙන්න.</t>
   </si>
   <si>
@@ -115,9 +133,15 @@
     <t>Neg_0009</t>
   </si>
   <si>
+    <t>hri man ennam.</t>
+  </si>
+  <si>
     <t>හරි මම එන්නම්.</t>
   </si>
   <si>
+    <t>හරි මන් එන්නම්.</t>
+  </si>
+  <si>
     <t>Neg_0010</t>
   </si>
   <si>
@@ -130,30 +154,48 @@
     <t>ටිකක් ටිකක් තේරුණා.</t>
   </si>
   <si>
-    <t>ටිකක් ටිකක් තේරුනා.</t>
-  </si>
-  <si>
     <t>Neg_0012</t>
   </si>
   <si>
+    <t>ep ep dn kata karnna epa.</t>
+  </si>
+  <si>
     <t>එපා එපා දැන් කතා කරන්න එපා.</t>
   </si>
   <si>
+    <t>එපා එපා දැන් කට කරන්න එපා.</t>
+  </si>
+  <si>
     <t>Neg_0013</t>
   </si>
   <si>
+    <t>aye mehma une?</t>
+  </si>
+  <si>
     <t>ඇයි මෙහෙම උනේ?</t>
   </si>
   <si>
+    <t>ආයෙ මෙහෙම උනේ?</t>
+  </si>
+  <si>
     <t>Neg_0014</t>
   </si>
   <si>
+    <t>ane... mt ak amthka una!</t>
+  </si>
+  <si>
     <t>අනේ... මට ඒක අමතක උනා!</t>
   </si>
   <si>
+    <t>අනේ... මට ඒක අමතක වුණා!</t>
+  </si>
+  <si>
     <t>Neg_0015</t>
   </si>
   <si>
+    <t>mn oyt heta msg ekk dnnm.</t>
+  </si>
+  <si>
     <t>මං ඔයාට හෙට msg එකක් දාන්නම්.</t>
   </si>
   <si>
@@ -163,15 +205,27 @@
     <t>Neg_0016</t>
   </si>
   <si>
+    <t>oyge gedr kuda inne?</t>
+  </si>
+  <si>
     <t>ඔයාගේ ගෙදර කවුද ඉන්නේ?</t>
   </si>
   <si>
+    <t>ඔයාගේ ගෙදර කුඩා ඉන්නේ?</t>
+  </si>
+  <si>
     <t>Neg_0017</t>
   </si>
   <si>
+    <t>man ada lunch eka gedarin genawa.</t>
+  </si>
+  <si>
     <t>මම අද lunch එක ගෙදරින් ගෙනාවා.</t>
   </si>
   <si>
+    <t>මං අද lunch එක ගෙදරින් ගෙනාවා.</t>
+  </si>
+  <si>
     <t>Neg_0018</t>
   </si>
   <si>
@@ -181,24 +235,42 @@
     <t>Neg_0019</t>
   </si>
   <si>
+    <t>man dn ready to go inne.</t>
+  </si>
+  <si>
     <t>මම දැන් ready to go ඉන්නේ.</t>
   </si>
   <si>
+    <t>මං දැන් ready to go ඉන්නේ.</t>
+  </si>
+  <si>
     <t>Neg_0020</t>
   </si>
   <si>
+    <t>oya please wait karann mma enkn.</t>
+  </si>
+  <si>
     <t>ඔයා please wait කරන්න මම එනකන්.</t>
   </si>
   <si>
+    <t>ඔයා please wait කරන්න මම එන්කන්.</t>
+  </si>
+  <si>
     <t>Neg_0021</t>
   </si>
   <si>
+    <t>mge email ek update karnn.</t>
+  </si>
+  <si>
     <t>මගේ email එක update කරන්න.</t>
   </si>
   <si>
     <t>Neg_0022</t>
   </si>
   <si>
+    <t>password ek reset krnna puluwanda?</t>
+  </si>
+  <si>
     <t>password එක reset කරන්න පුළුවන්ද?</t>
   </si>
   <si>
@@ -211,16 +283,25 @@
     <t>Neg_0024</t>
   </si>
   <si>
+    <t>Telegram group akt msg ekk danna.</t>
+  </si>
+  <si>
     <t>Telegram group එකට msg එකක් දාන්න.</t>
   </si>
   <si>
+    <t>Telegram group akt msg එකක් දාන්න.</t>
+  </si>
+  <si>
     <t>Neg_0025</t>
   </si>
   <si>
+    <t>CV ek PDF widihta upload karnna.</t>
+  </si>
+  <si>
     <t>CV එක PDF විදිහට upload කරන්න.</t>
   </si>
   <si>
-    <t>CV ඒක PDF විදිහට upload කරන්න.</t>
+    <t>CV එක් PDF විදිහට upload කරන්න.</t>
   </si>
   <si>
     <t>Neg_0026</t>
@@ -250,12 +331,21 @@
     <t>Neg_0030</t>
   </si>
   <si>
+    <t>mn Colombo Fort eken bus ekata nagga.</t>
+  </si>
+  <si>
     <t>මම Colombo Fort එකෙන් bus එකට නැග්ගා.</t>
   </si>
   <si>
+    <t>මන් Colombo Fort එකෙන් bus එකට නැග්ගා.</t>
+  </si>
+  <si>
     <t>Neg_0031</t>
   </si>
   <si>
+    <t>Kasun ada exam ekt awe na.</t>
+  </si>
+  <si>
     <t>Kasun අද exam එකට ආවේ නෑ.</t>
   </si>
   <si>
@@ -265,27 +355,39 @@
     <t>Neg_0032</t>
   </si>
   <si>
+    <t>Nethmi presentation ek lssnt kala.</t>
+  </si>
+  <si>
     <t>Nethmi presentation එක ලස්සනට කළා.</t>
   </si>
   <si>
-    <t>නැත්නම් presentation එක ලස්සනට කළා.</t>
+    <t>නැත්නම් presentation එක ලස්සනයි කළා.</t>
   </si>
   <si>
     <t>Neg_0033</t>
   </si>
   <si>
+    <t>mt 2nd attempt ekt register wenna one.</t>
+  </si>
+  <si>
     <t>මට 2nd attempt එකට register වෙන්න ඕනේ.</t>
   </si>
   <si>
     <t>Neg_0034</t>
   </si>
   <si>
+    <t>lamai 25k class ekt awa.</t>
+  </si>
+  <si>
     <t>ළමයි 25ක් class එකට ආවා.</t>
   </si>
   <si>
     <t>Neg_0035</t>
   </si>
   <si>
+    <t>mt Rs. 1500k transfer krnna.</t>
+  </si>
+  <si>
     <t>මට Rs. 1500ක් transfer කරන්න.</t>
   </si>
   <si>
@@ -301,12 +403,18 @@
     <t>Neg_0037</t>
   </si>
   <si>
+    <t>class ek 8.30pm ptn gnnawa.</t>
+  </si>
+  <si>
     <t>class එක 8.30pm පටන් ගන්නවා.</t>
   </si>
   <si>
     <t>Neg_0038</t>
   </si>
   <si>
+    <t>mt 10:15AM wlt mtk krnna.</t>
+  </si>
+  <si>
     <t>මට 10:15AM වෙලාවට මතක් කරන්න.</t>
   </si>
   <si>
@@ -316,6 +424,9 @@
     <t>Neg_0039</t>
   </si>
   <si>
+    <t>exam ek 2026-05-12 wenida thiyenwa.</t>
+  </si>
+  <si>
     <t>exam එක 2026-05-12 වෙනිදා තියෙනවා.</t>
   </si>
   <si>
@@ -328,9 +439,15 @@
     <t>Neg_0041</t>
   </si>
   <si>
+    <t>mt 500g sini genna.</t>
+  </si>
+  <si>
     <t>මට 500g සීනි ගේන්න.</t>
   </si>
   <si>
+    <t>මට 500g සිනි ගෙන්න.</t>
+  </si>
+  <si>
     <t>Neg_0042</t>
   </si>
   <si>
@@ -340,6 +457,9 @@
     <t>Neg_0043</t>
   </si>
   <si>
+    <t>ptt machan oya wede goda dgththa.</t>
+  </si>
+  <si>
     <t>පට්ට මචං ඔයා වැඩේ ගොඩ දාගත්තා.</t>
   </si>
   <si>
@@ -349,12 +469,18 @@
     <t>Neg_0044</t>
   </si>
   <si>
+    <t>ado mt podi help ekk one.</t>
+  </si>
+  <si>
     <t>අඩෝ මට පොඩි help එකක් ඕනේ.</t>
   </si>
   <si>
     <t>Neg_0045</t>
   </si>
   <si>
+    <t>me link ek open krnna: https://sliit.lk</t>
+  </si>
+  <si>
     <t>මේ link එක open කරන්න: https://sliit.lk</t>
   </si>
   <si>
@@ -364,6 +490,9 @@
     <t>Neg_0046</t>
   </si>
   <si>
+    <t>mt email ekk danna: raki2026@gmail.com</t>
+  </si>
+  <si>
     <t>මට email එකක් දාන්න: raki2026@gmail.com</t>
   </si>
   <si>
@@ -382,7 +511,7 @@
     <t>ඔයා වැඩේ හොඳට කළා ❤️</t>
   </si>
   <si>
-    <t>ඔය වැඩේ හොදට කළා ❤️</t>
+    <t>ඔය වැඩේ හොඳට කළා ❤️</t>
   </si>
   <si>
     <t>Neg_0049</t>
@@ -400,6 +529,9 @@
     <t>මචං හෙට 9.00am Zoom meeting එකට කලින් report එක PDF විදිහට upload කරන්න. link එක email එකෙන් එවන්න පුලුවන්නම් ලොකු දෙයක්. මම ගෙදරින් එන්න කලින් file එක බලලා mistakes තියෙනවානම් correct කරන්න ඕනේ. Please confirm after uploading, නැත්නම් මට WhatsApp message එකක් දාන්න. Thanks මචන්.</t>
   </si>
   <si>
+    <t>UI Error</t>
+  </si>
+  <si>
     <t>Neg_0050</t>
   </si>
   <si>
@@ -409,151 +541,82 @@
     <t>අඩෝ Saturday දවසේ Kandy trip එකට 12 දෙනෙක් යනවා. Rs. 3000ක් අරන් එන්න, location එක WhatsApp group එකට දාන්නම්. ඔයාගේ ID card එක අමතක කරන්න එපා. bus එක 6:45AM වෙලාවට පිටත් වෙනවා, late උනොත් call එකක් දෙන්න. map link එක email කරන්නම්: trip2026@gmail.com 😎 අපි set එක ආවම attendance list එක Google Sheet එකේ update කරන්න, පස්සේ photos ටික Drive folder එකට upload කරන්න.</t>
   </si>
   <si>
-    <t>අඩෝ Saturday දවසේ Kandy trip එකට 12 දෙනෙක් යනවා. Rs. 3000ක් අරන් එන්න, location එක WhatsApp group එකට දාන්නම්. ඔයාගේ ID කාඩ් එක අමතක කරන්න එපා. bus එක 6:45AM වලට පිටත් වෙනවා, late උනොත් call එකක් දෙන්න. map link එක email කරන්නම්: trip2026@gmail.කොම් 😎 අපි set එක ආවම attendance list එක Google Sheet එකේ update කරන්න, පස්සේ photos ටික Drive folder එකට upload කරන්න.</t>
-  </si>
-  <si>
-    <t>oyge nama mokkda?</t>
-  </si>
-  <si>
-    <t>ada class ek tiyenwada?</t>
-  </si>
-  <si>
-    <t>dnm gedrta ynn.</t>
-  </si>
-  <si>
-    <t>mek copy krl group akt dnna.</t>
-  </si>
-  <si>
-    <t>sub udasanak yaluwa!</t>
-  </si>
-  <si>
-    <t>sub udeyk hamotama!</t>
-  </si>
-  <si>
-    <t>puluwnnam mt call ekk denna.</t>
-  </si>
-  <si>
-    <t>karunkarala report ek ada ewnna.</t>
-  </si>
-  <si>
-    <t>hri man ennam.</t>
-  </si>
-  <si>
-    <t>ow ek hari.</t>
-  </si>
-  <si>
-    <t>tikk tikk teruna.</t>
-  </si>
-  <si>
-    <t>ep ep dn kata karnna epa.</t>
-  </si>
-  <si>
-    <t>aye mehma une?</t>
-  </si>
-  <si>
-    <t>ane... mt ak amthka una!</t>
-  </si>
-  <si>
-    <t>mn oyt heta msg ekk dnnm.</t>
-  </si>
-  <si>
-    <t>oyge gedr kuda inne?</t>
-  </si>
-  <si>
-    <t>man ada lunch eka gedarin genawa.</t>
-  </si>
-  <si>
-    <t>ape sir assignment ek check kl.</t>
-  </si>
-  <si>
-    <t>man dn ready to go inne.</t>
-  </si>
-  <si>
-    <t>oya please wait karann mma enkn.</t>
-  </si>
-  <si>
-    <t>mge email ek update karnn.</t>
-  </si>
-  <si>
-    <t>password ek reset krnna puluwanda?</t>
-  </si>
-  <si>
-    <t>Teams meeting ak heta thiyenawa.</t>
-  </si>
-  <si>
-    <t>Telegram group akt msg ekk danna.</t>
-  </si>
-  <si>
-    <t>CV ek PDF widihta upload karnna.</t>
-  </si>
-  <si>
-    <t>ID card ek scan karla ewnna.</t>
-  </si>
-  <si>
-    <t>het practical ekta enna.</t>
-  </si>
-  <si>
-    <t>lab report ek submit karda?</t>
-  </si>
-  <si>
-    <t>api heta Kandy wlt ynawa.</t>
-  </si>
-  <si>
-    <t>mn Colombo Fort eken bus ekata nagga.</t>
-  </si>
-  <si>
-    <t>Kasun ada exam ekt awe na.</t>
-  </si>
-  <si>
-    <t>Nethmi presentation ek lssnt kala.</t>
-  </si>
-  <si>
-    <t>mt 2nd attempt ekt register wenna one.</t>
-  </si>
-  <si>
-    <t>lamai 25k class ekt awa.</t>
-  </si>
-  <si>
-    <t>mt Rs. 1500k transfer krnna.</t>
-  </si>
-  <si>
-    <t>Dollar 20k gewnna una.</t>
-  </si>
-  <si>
-    <t>class ek 8.30pm ptn gnnawa.</t>
-  </si>
-  <si>
-    <t>mt 10:15AM wlt mtk krnna.</t>
-  </si>
-  <si>
-    <t>exam ek 2026-05-12 wenida thiyenwa.</t>
-  </si>
-  <si>
-    <t>assignment ek March 3t klin denna.</t>
-  </si>
-  <si>
-    <t>mt 500g sini genna.</t>
-  </si>
-  <si>
-    <t>bike ek 5km witra giya.</t>
-  </si>
-  <si>
-    <t>ptt machan oya wede goda dgththa.</t>
-  </si>
-  <si>
-    <t>ado mt podi help ekk one.</t>
-  </si>
-  <si>
-    <t>me link ek open krnna: https://sliit.lk</t>
-  </si>
-  <si>
-    <t>mt email ekk danna: raki2026@gmail.com</t>
-  </si>
-  <si>
-    <t>mt dn hina ynwa 😂</t>
-  </si>
-  <si>
-    <t>oya wede hodt kala ❤️</t>
+    <t>oyge nma mkkda?</t>
+  </si>
+  <si>
+    <t>ad clss ek tiyenwad?</t>
+  </si>
+  <si>
+    <t>karunkarla report ek ad evnna.</t>
+  </si>
+  <si>
+    <t>ow eak hri.</t>
+  </si>
+  <si>
+    <t>tikkk tikk terunA.</t>
+  </si>
+  <si>
+    <t>ape sir assignment ek check kr.</t>
+  </si>
+  <si>
+    <t>Teams meeting ak het teyenawa.</t>
+  </si>
+  <si>
+    <t>Teams මීටින් එක හෙට තියෙනවා.</t>
+  </si>
+  <si>
+    <t>ID card ek scan krl awnna.</t>
+  </si>
+  <si>
+    <t>het practical eakta enn.</t>
+  </si>
+  <si>
+    <t>lab රිපොර්ට් එක submit කරාද?</t>
+  </si>
+  <si>
+    <t>lab report ek submit krda?</t>
+  </si>
+  <si>
+    <t>api het Kandy wlt ynawa.</t>
+  </si>
+  <si>
+    <t>අපි හෙට නුවර වලට යනවා.</t>
+  </si>
+  <si>
+    <t>මට 2nd attempt එකට රෙජිස්ටර් වෙන්න ඕනේ.</t>
+  </si>
+  <si>
+    <t>ළමයි 25ක් ක්ලාස් එකට ආවා.</t>
+  </si>
+  <si>
+    <t>මට Rs. 1500ක් ට්‍රාන්ස්වර් කරන්න.</t>
+  </si>
+  <si>
+    <t>Dollar 20k gewnn una.</t>
+  </si>
+  <si>
+    <t>ක්ලාස් එක 8.30pm පටන් ගන්නවා.</t>
+  </si>
+  <si>
+    <t>එක්සෑම් එක 2026-05-12 වෙනිදා තියෙනවා.</t>
+  </si>
+  <si>
+    <t>Assignment එක March 3ට කලින් දෙන්න.</t>
+  </si>
+  <si>
+    <t>assignment ak March 3t klen denna.</t>
+  </si>
+  <si>
+    <t>bike aek 5km witr giya.</t>
+  </si>
+  <si>
+    <t>අඩෝ මට පොඩි හෙල්ප් එකක් ඕනේ.</t>
+  </si>
+  <si>
+    <t>mt dn hena ynv 😂</t>
+  </si>
+  <si>
+    <t>oya vede hodt kala ❤️</t>
   </si>
 </sst>
 </file>
@@ -1032,16 +1095,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1070,22 +1133,22 @@
     </row>
     <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1114,22 +1177,22 @@
     </row>
     <row r="10" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1158,22 +1221,22 @@
     </row>
     <row r="14" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1202,22 +1265,22 @@
     </row>
     <row r="18" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1246,22 +1309,22 @@
     </row>
     <row r="22" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1290,22 +1353,22 @@
     </row>
     <row r="26" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1334,22 +1397,22 @@
     </row>
     <row r="30" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1378,22 +1441,22 @@
     </row>
     <row r="34" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1422,22 +1485,22 @@
     </row>
     <row r="38" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1466,22 +1529,22 @@
     </row>
     <row r="42" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1510,22 +1573,22 @@
     </row>
     <row r="46" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1554,22 +1617,22 @@
     </row>
     <row r="50" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1598,22 +1661,22 @@
     </row>
     <row r="54" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1642,22 +1705,22 @@
     </row>
     <row r="58" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1686,22 +1749,22 @@
     </row>
     <row r="62" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>145</v>
+        <v>61</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1730,22 +1793,22 @@
     </row>
     <row r="66" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>146</v>
+        <v>65</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1774,22 +1837,22 @@
     </row>
     <row r="70" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1818,22 +1881,22 @@
     </row>
     <row r="74" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>148</v>
+        <v>71</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1862,22 +1925,22 @@
     </row>
     <row r="78" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1906,22 +1969,22 @@
     </row>
     <row r="82" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1950,22 +2013,22 @@
     </row>
     <row r="86" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1994,22 +2057,22 @@
     </row>
     <row r="90" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2038,22 +2101,22 @@
     </row>
     <row r="94" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2082,22 +2145,22 @@
     </row>
     <row r="98" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>154</v>
+        <v>91</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2126,22 +2189,22 @@
     </row>
     <row r="102" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2170,22 +2233,22 @@
     </row>
     <row r="106" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2214,22 +2277,22 @@
     </row>
     <row r="110" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2258,22 +2321,22 @@
     </row>
     <row r="114" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2302,22 +2365,22 @@
     </row>
     <row r="118" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2346,22 +2409,22 @@
     </row>
     <row r="122" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2390,22 +2453,22 @@
     </row>
     <row r="126" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>161</v>
+        <v>111</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2434,22 +2497,22 @@
     </row>
     <row r="130" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2478,22 +2541,22 @@
     </row>
     <row r="134" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2522,22 +2585,22 @@
     </row>
     <row r="138" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2566,22 +2629,22 @@
     </row>
     <row r="142" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2610,22 +2673,22 @@
     </row>
     <row r="146" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>93</v>
+        <v>191</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2654,22 +2717,22 @@
     </row>
     <row r="150" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2698,22 +2761,22 @@
     </row>
     <row r="154" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2742,22 +2805,22 @@
     </row>
     <row r="158" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2786,22 +2849,22 @@
     </row>
     <row r="162" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2830,22 +2893,22 @@
     </row>
     <row r="166" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2874,22 +2937,22 @@
     </row>
     <row r="170" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2918,22 +2981,22 @@
     </row>
     <row r="174" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2962,22 +3025,22 @@
     </row>
     <row r="178" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3006,22 +3069,22 @@
     </row>
     <row r="182" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="F182" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3050,22 +3113,22 @@
     </row>
     <row r="186" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F186" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3094,22 +3157,22 @@
     </row>
     <row r="190" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3138,22 +3201,22 @@
     </row>
     <row r="194" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>10</v>
+        <v>169</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3182,22 +3245,22 @@
     </row>
     <row r="198" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3226,6 +3289,9 @@
     </row>
   </sheetData>
   <mergeCells count="300">
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="E62:E65"/>
     <mergeCell ref="F194:F197"/>
     <mergeCell ref="A198:A201"/>
     <mergeCell ref="C198:C201"/>
@@ -3240,13 +3306,16 @@
     <mergeCell ref="E182:E185"/>
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="F106:F109"/>
+    <mergeCell ref="F186:F189"/>
     <mergeCell ref="A190:A193"/>
     <mergeCell ref="C150:C153"/>
-    <mergeCell ref="F186:F189"/>
     <mergeCell ref="C190:C193"/>
     <mergeCell ref="B114:B117"/>
     <mergeCell ref="D114:D117"/>
     <mergeCell ref="B154:B157"/>
+    <mergeCell ref="C174:C177"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="B138:B141"/>
     <mergeCell ref="D6:D9"/>
     <mergeCell ref="C26:C29"/>
     <mergeCell ref="D190:D193"/>
@@ -3268,10 +3337,9 @@
     <mergeCell ref="E34:E37"/>
     <mergeCell ref="B182:B185"/>
     <mergeCell ref="D134:D137"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="F134:F137"/>
     <mergeCell ref="E22:E25"/>
+    <mergeCell ref="D74:D77"/>
     <mergeCell ref="C194:C197"/>
     <mergeCell ref="C38:C41"/>
     <mergeCell ref="D58:D61"/>
@@ -3293,34 +3361,27 @@
     <mergeCell ref="C170:C173"/>
     <mergeCell ref="F78:F81"/>
     <mergeCell ref="F118:F121"/>
-    <mergeCell ref="C174:C177"/>
-    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="F158:F161"/>
     <mergeCell ref="B190:B193"/>
     <mergeCell ref="D194:D197"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="E86:E89"/>
-    <mergeCell ref="B34:B37"/>
     <mergeCell ref="F38:F41"/>
     <mergeCell ref="A42:A45"/>
     <mergeCell ref="B74:B77"/>
     <mergeCell ref="F50:F53"/>
     <mergeCell ref="E162:E165"/>
     <mergeCell ref="D130:D133"/>
+    <mergeCell ref="A14:A17"/>
     <mergeCell ref="A134:A137"/>
     <mergeCell ref="B162:B165"/>
     <mergeCell ref="F130:F133"/>
-    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="E18:E21"/>
     <mergeCell ref="E134:E137"/>
     <mergeCell ref="D138:D141"/>
     <mergeCell ref="F54:F57"/>
     <mergeCell ref="C158:C161"/>
-    <mergeCell ref="F190:F193"/>
-    <mergeCell ref="E190:E193"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="F134:F137"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="C118:C121"/>
     <mergeCell ref="F154:F157"/>
     <mergeCell ref="A158:A161"/>
     <mergeCell ref="D186:D189"/>
@@ -3343,6 +3404,8 @@
     <mergeCell ref="D146:D149"/>
     <mergeCell ref="E166:E169"/>
     <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="E86:E89"/>
     <mergeCell ref="B198:B201"/>
     <mergeCell ref="D14:D17"/>
     <mergeCell ref="A106:A109"/>
@@ -3367,18 +3430,9 @@
     <mergeCell ref="A110:A113"/>
     <mergeCell ref="F162:F165"/>
     <mergeCell ref="B94:B97"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="D158:D161"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="D154:D157"/>
-    <mergeCell ref="C162:C165"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="F158:F161"/>
-    <mergeCell ref="E62:E65"/>
-    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="F190:F193"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C138:C141"/>
     <mergeCell ref="C178:C181"/>
     <mergeCell ref="E54:E57"/>
     <mergeCell ref="D30:D33"/>
@@ -3392,6 +3446,14 @@
     <mergeCell ref="C58:C61"/>
     <mergeCell ref="E58:E61"/>
     <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="E190:E193"/>
+    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="D154:D157"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="B42:B45"/>
@@ -3416,6 +3478,7 @@
     <mergeCell ref="C70:C73"/>
     <mergeCell ref="E70:E73"/>
     <mergeCell ref="C46:C49"/>
+    <mergeCell ref="B194:B197"/>
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="B90:B93"/>
     <mergeCell ref="D50:D53"/>
@@ -3426,6 +3489,7 @@
     <mergeCell ref="E150:E153"/>
     <mergeCell ref="D178:D181"/>
     <mergeCell ref="D34:D37"/>
+    <mergeCell ref="A182:A185"/>
     <mergeCell ref="F178:F181"/>
     <mergeCell ref="C42:C45"/>
     <mergeCell ref="F34:F37"/>
@@ -3434,19 +3498,13 @@
     <mergeCell ref="E42:E45"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B106:B109"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="A30:A33"/>
     <mergeCell ref="E186:E189"/>
     <mergeCell ref="C106:C109"/>
     <mergeCell ref="A194:A197"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B158:B161"/>
-    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="D78:D81"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="E2:E5"/>
@@ -3464,6 +3522,41 @@
     <mergeCell ref="C66:C69"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="E66:E69"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="F150:F153"/>
+    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="E154:E157"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="E130:E133"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
     <mergeCell ref="D198:D201"/>
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A146:A149"/>
@@ -3474,58 +3567,28 @@
     <mergeCell ref="A178:A181"/>
     <mergeCell ref="D126:D129"/>
     <mergeCell ref="C94:C97"/>
+    <mergeCell ref="A74:A77"/>
     <mergeCell ref="F126:F129"/>
     <mergeCell ref="D166:D169"/>
     <mergeCell ref="E94:E97"/>
     <mergeCell ref="E90:E93"/>
     <mergeCell ref="F110:F113"/>
     <mergeCell ref="D150:D153"/>
-    <mergeCell ref="F150:F153"/>
-    <mergeCell ref="E158:E161"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="E154:E157"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="E130:E133"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="F82:F85"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E74:E77"/>
-    <mergeCell ref="A118:A121"/>
     <mergeCell ref="C14:C17"/>
     <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C154:C157"/>
     <mergeCell ref="C98:C101"/>
-    <mergeCell ref="C154:C157"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="A166:A169"/>
     <mergeCell ref="E102:E105"/>
     <mergeCell ref="B50:B53"/>
     <mergeCell ref="A162:A165"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="C162:C165"/>
+    <mergeCell ref="B130:B133"/>
     <mergeCell ref="B38:B41"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C138:C141"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="B34:B37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SLIIT\3year1sem\ITPM\Test assign\test_automation\IT3040-Assignment1-Singlish-Transliteration-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDBAAD27-7A9D-4FE8-8839-21D9E3C7795C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCE9E8C-8C42-46E6-80AC-A50F9510B102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="208">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -46,18 +46,27 @@
     <t>S</t>
   </si>
   <si>
+    <t>oyge nma mkkda?</t>
+  </si>
+  <si>
     <t>ඔයාගේ නම මොකක්ද?</t>
   </si>
   <si>
+    <t>ඔයාගේ නම් මොකක්ද?</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Neg_0002</t>
+  </si>
+  <si>
+    <t>අද class එක තියෙනවද?</t>
+  </si>
+  <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>Neg_0002</t>
-  </si>
-  <si>
-    <t>අද class එක තියෙනවද?</t>
-  </si>
-  <si>
     <t>Neg_0003</t>
   </si>
   <si>
@@ -70,9 +79,6 @@
     <t>දැන් ගෙදරට යන්න.</t>
   </si>
   <si>
-    <t>FAIL</t>
-  </si>
-  <si>
     <t>Neg_0004</t>
   </si>
   <si>
@@ -127,6 +133,9 @@
     <t>Neg_0008</t>
   </si>
   <si>
+    <t>karunkarla report ek ad evnna.</t>
+  </si>
+  <si>
     <t>කරුණාකරලා report එක අද එවන්න.</t>
   </si>
   <si>
@@ -229,9 +238,15 @@
     <t>Neg_0018</t>
   </si>
   <si>
+    <t>ape sir assignment ek check kr.</t>
+  </si>
+  <si>
     <t>අපේ sir assignment එක check කළා.</t>
   </si>
   <si>
+    <t>අපේ sir assignment එක check කරා.</t>
+  </si>
+  <si>
     <t>Neg_0019</t>
   </si>
   <si>
@@ -259,24 +274,24 @@
     <t>Neg_0021</t>
   </si>
   <si>
-    <t>mge email ek update karnn.</t>
-  </si>
-  <si>
     <t>මගේ email එක update කරන්න.</t>
   </si>
   <si>
     <t>Neg_0022</t>
   </si>
   <si>
-    <t>password ek reset krnna puluwanda?</t>
-  </si>
-  <si>
     <t>password එක reset කරන්න පුළුවන්ද?</t>
   </si>
   <si>
     <t>Neg_0023</t>
   </si>
   <si>
+    <t>Teams meeting ak het teyenawa.</t>
+  </si>
+  <si>
+    <t>Teams මීටින් එක හෙට තියෙනවා.</t>
+  </si>
+  <si>
     <t>Teams meeting එක හෙට තියෙනවා.</t>
   </si>
   <si>
@@ -307,24 +322,48 @@
     <t>Neg_0026</t>
   </si>
   <si>
+    <t>ID card ek scan krl awnna.</t>
+  </si>
+  <si>
     <t>ID card එක scan කරලා එවන්න.</t>
   </si>
   <si>
+    <t>ID card එක scan කරලා අව්වන්න.</t>
+  </si>
+  <si>
     <t>Neg_0027</t>
   </si>
   <si>
+    <t>het practical eakta enn.</t>
+  </si>
+  <si>
     <t>හෙට practical එකට එන්න.</t>
   </si>
   <si>
+    <t>හෙට ප්රසිටල් එකකට එන්න.</t>
+  </si>
+  <si>
     <t>Neg_0028</t>
   </si>
   <si>
+    <t>lab report ek submit krda?</t>
+  </si>
+  <si>
+    <t>lab රිපොර්ට් එක submit කරාද?</t>
+  </si>
+  <si>
     <t>lab report එක submit කරාද?</t>
   </si>
   <si>
     <t>Neg_0029</t>
   </si>
   <si>
+    <t>api het Kandy wlt ynawa.</t>
+  </si>
+  <si>
+    <t>අපි හෙට නුවර වලට යනවා.</t>
+  </si>
+  <si>
     <t>අපි හෙට Kandy වලට යනවා.</t>
   </si>
   <si>
@@ -370,6 +409,9 @@
     <t>mt 2nd attempt ekt register wenna one.</t>
   </si>
   <si>
+    <t>මට 2nd attempt එකට රෙජිස්ටර් වෙන්න ඕනේ.</t>
+  </si>
+  <si>
     <t>මට 2nd attempt එකට register වෙන්න ඕනේ.</t>
   </si>
   <si>
@@ -379,6 +421,9 @@
     <t>lamai 25k class ekt awa.</t>
   </si>
   <si>
+    <t>ළමයි 25ක් ක්ලාස් එකට ආවා.</t>
+  </si>
+  <si>
     <t>ළමයි 25ක් class එකට ආවා.</t>
   </si>
   <si>
@@ -388,12 +433,18 @@
     <t>mt Rs. 1500k transfer krnna.</t>
   </si>
   <si>
+    <t>මට Rs. 1500ක් ට්‍රාන්ස්වර් කරන්න.</t>
+  </si>
+  <si>
     <t>මට Rs. 1500ක් transfer කරන්න.</t>
   </si>
   <si>
     <t>Neg_0036</t>
   </si>
   <si>
+    <t>Dollar 20k gewnn una.</t>
+  </si>
+  <si>
     <t>dollar 20ක් ගෙවන්න උනා.</t>
   </si>
   <si>
@@ -406,6 +457,9 @@
     <t>class ek 8.30pm ptn gnnawa.</t>
   </si>
   <si>
+    <t>ක්ලාස් එක 8.30pm පටන් ගන්නවා.</t>
+  </si>
+  <si>
     <t>class එක 8.30pm පටන් ගන්නවා.</t>
   </si>
   <si>
@@ -427,13 +481,22 @@
     <t>exam ek 2026-05-12 wenida thiyenwa.</t>
   </si>
   <si>
+    <t>එක්සෑම් එක 2026-05-12 වෙනිදා තියෙනවා.</t>
+  </si>
+  <si>
     <t>exam එක 2026-05-12 වෙනිදා තියෙනවා.</t>
   </si>
   <si>
     <t>Neg_0040</t>
   </si>
   <si>
-    <t>assignment එක March 3ට කලින් දෙන්න.</t>
+    <t>assignment ak March 3t klen denna.</t>
+  </si>
+  <si>
+    <t>Assignment එක March 3ට කලින් දෙන්න.</t>
+  </si>
+  <si>
+    <t>assignment එක මාර්තු 3ට ක්ලෙන් දෙන්න.</t>
   </si>
   <si>
     <t>Neg_0041</t>
@@ -451,9 +514,15 @@
     <t>Neg_0042</t>
   </si>
   <si>
+    <t>bike aek 5km witr giya.</t>
+  </si>
+  <si>
     <t>bike එක 5km විතර ගියා.</t>
   </si>
   <si>
+    <t>bike අෙක් 5km විතර ගියා.</t>
+  </si>
+  <si>
     <t>Neg_0043</t>
   </si>
   <si>
@@ -472,6 +541,9 @@
     <t>ado mt podi help ekk one.</t>
   </si>
   <si>
+    <t>අඩෝ මට පොඩි හෙල්ප් එකක් ඕනේ.</t>
+  </si>
+  <si>
     <t>අඩෝ මට පොඩි help එකක් ඕනේ.</t>
   </si>
   <si>
@@ -502,16 +574,25 @@
     <t>Neg_0047</t>
   </si>
   <si>
+    <t>mt dn hena ynv 😂</t>
+  </si>
+  <si>
     <t>මට දැන් හිනා යනවා 😂</t>
   </si>
   <si>
+    <t>මට දැන් හෙන යනවා 😂</t>
+  </si>
+  <si>
     <t>Neg_0048</t>
   </si>
   <si>
+    <t>oya vede hodt kala ❤️</t>
+  </si>
+  <si>
     <t>ඔයා වැඩේ හොඳට කළා ❤️</t>
   </si>
   <si>
-    <t>ඔය වැඩේ හොඳට කළා ❤️</t>
+    <t>ඔයා වැඩෙ හොඳට කළා ❤️</t>
   </si>
   <si>
     <t>Neg_0049</t>
@@ -529,9 +610,6 @@
     <t>මචං හෙට 9.00am Zoom meeting එකට කලින් report එක PDF විදිහට upload කරන්න. link එක email එකෙන් එවන්න පුලුවන්නම් ලොකු දෙයක්. මම ගෙදරින් එන්න කලින් file එක බලලා mistakes තියෙනවානම් correct කරන්න ඕනේ. Please confirm after uploading, නැත්නම් මට WhatsApp message එකක් දාන්න. Thanks මචන්.</t>
   </si>
   <si>
-    <t>UI Error</t>
-  </si>
-  <si>
     <t>Neg_0050</t>
   </si>
   <si>
@@ -541,82 +619,31 @@
     <t>අඩෝ Saturday දවසේ Kandy trip එකට 12 දෙනෙක් යනවා. Rs. 3000ක් අරන් එන්න, location එක WhatsApp group එකට දාන්නම්. ඔයාගේ ID card එක අමතක කරන්න එපා. bus එක 6:45AM වෙලාවට පිටත් වෙනවා, late උනොත් call එකක් දෙන්න. map link එක email කරන්නම්: trip2026@gmail.com 😎 අපි set එක ආවම attendance list එක Google Sheet එකේ update කරන්න, පස්සේ photos ටික Drive folder එකට upload කරන්න.</t>
   </si>
   <si>
-    <t>oyge nma mkkda?</t>
-  </si>
-  <si>
-    <t>ad clss ek tiyenwad?</t>
-  </si>
-  <si>
-    <t>karunkarla report ek ad evnna.</t>
-  </si>
-  <si>
-    <t>ow eak hri.</t>
-  </si>
-  <si>
-    <t>tikkk tikk terunA.</t>
-  </si>
-  <si>
-    <t>ape sir assignment ek check kr.</t>
-  </si>
-  <si>
-    <t>Teams meeting ak het teyenawa.</t>
-  </si>
-  <si>
-    <t>Teams මීටින් එක හෙට තියෙනවා.</t>
-  </si>
-  <si>
-    <t>ID card ek scan krl awnna.</t>
-  </si>
-  <si>
-    <t>het practical eakta enn.</t>
-  </si>
-  <si>
-    <t>lab රිපොර්ට් එක submit කරාද?</t>
-  </si>
-  <si>
-    <t>lab report ek submit krda?</t>
-  </si>
-  <si>
-    <t>api het Kandy wlt ynawa.</t>
-  </si>
-  <si>
-    <t>අපි හෙට නුවර වලට යනවා.</t>
-  </si>
-  <si>
-    <t>මට 2nd attempt එකට රෙජිස්ටර් වෙන්න ඕනේ.</t>
-  </si>
-  <si>
-    <t>ළමයි 25ක් ක්ලාස් එකට ආවා.</t>
-  </si>
-  <si>
-    <t>මට Rs. 1500ක් ට්‍රාන්ස්වර් කරන්න.</t>
-  </si>
-  <si>
-    <t>Dollar 20k gewnn una.</t>
-  </si>
-  <si>
-    <t>ක්ලාස් එක 8.30pm පටන් ගන්නවා.</t>
-  </si>
-  <si>
-    <t>එක්සෑම් එක 2026-05-12 වෙනිදා තියෙනවා.</t>
-  </si>
-  <si>
-    <t>Assignment එක March 3ට කලින් දෙන්න.</t>
-  </si>
-  <si>
-    <t>assignment ak March 3t klen denna.</t>
-  </si>
-  <si>
-    <t>bike aek 5km witr giya.</t>
-  </si>
-  <si>
-    <t>අඩෝ මට පොඩි හෙල්ප් එකක් ඕනේ.</t>
-  </si>
-  <si>
-    <t>mt dn hena ynv 😂</t>
-  </si>
-  <si>
-    <t>oya vede hodt kala ❤️</t>
+    <t>අඩෝ Saturday දවසේ Kandy trip එකට 12 දෙනෙක් යනවා. Rs. 3000ක් අරන් එන්න, location එක WhatsApp group එකට දාන්නම්. ඔයාගේ ID කාඩ් එක අමතක කරන්න එපා. bus එක 6:45AM වලට පිටත් වෙනවා, late උනොත් call එකක් දෙන්න. map link එක email කරන්නම්: trip2026@gmail.කොම් 😎 අපි set එක ආවම attendance list එක Google Sheet එකේ update කරන්න, පස්සේ photos ටික Drive folder එකට upload කරන්න.</t>
+  </si>
+  <si>
+    <t>ad class ek tiyenwd?</t>
+  </si>
+  <si>
+    <t>අද ක්ලාස් එක තියෙනවද?</t>
+  </si>
+  <si>
+    <t>කරුණාකරලා රිපෝර්ට් එක අද එවන්න.</t>
+  </si>
+  <si>
+    <t>ow eke hri.</t>
+  </si>
+  <si>
+    <t>tikakk tikakk terunna.</t>
+  </si>
+  <si>
+    <t>mege email eke update krnn.</t>
+  </si>
+  <si>
+    <t>පාස්වර්ඩ් එක reset කරන්න පුළුවන්ද?</t>
+  </si>
+  <si>
+    <t>password eak reset krn puluwnda?</t>
   </si>
 </sst>
 </file>
@@ -1095,16 +1122,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>173</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1133,22 +1160,22 @@
     </row>
     <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1177,22 +1204,22 @@
     </row>
     <row r="10" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1221,22 +1248,22 @@
     </row>
     <row r="14" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1265,22 +1292,22 @@
     </row>
     <row r="18" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1309,22 +1336,22 @@
     </row>
     <row r="22" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1353,22 +1380,22 @@
     </row>
     <row r="26" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1397,22 +1424,22 @@
     </row>
     <row r="30" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>175</v>
+        <v>37</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>35</v>
+        <v>202</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1441,22 +1468,22 @@
     </row>
     <row r="34" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1485,22 +1512,22 @@
     </row>
     <row r="38" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1529,22 +1556,22 @@
     </row>
     <row r="42" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1573,22 +1600,22 @@
     </row>
     <row r="46" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1617,22 +1644,22 @@
     </row>
     <row r="50" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1661,22 +1688,22 @@
     </row>
     <row r="54" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1705,22 +1732,22 @@
     </row>
     <row r="58" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1749,22 +1776,22 @@
     </row>
     <row r="62" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1793,22 +1820,22 @@
     </row>
     <row r="66" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1837,22 +1864,22 @@
     </row>
     <row r="70" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1881,22 +1908,22 @@
     </row>
     <row r="74" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1925,22 +1952,22 @@
     </row>
     <row r="78" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1969,22 +1996,22 @@
     </row>
     <row r="82" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2013,22 +2040,22 @@
     </row>
     <row r="86" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2057,22 +2084,22 @@
     </row>
     <row r="90" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2101,22 +2128,22 @@
     </row>
     <row r="94" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2145,22 +2172,22 @@
     </row>
     <row r="98" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2189,22 +2216,22 @@
     </row>
     <row r="102" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2233,22 +2260,22 @@
     </row>
     <row r="106" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>182</v>
+        <v>104</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2277,22 +2304,22 @@
     </row>
     <row r="110" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2321,22 +2348,22 @@
     </row>
     <row r="114" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2365,22 +2392,22 @@
     </row>
     <row r="118" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2409,22 +2436,22 @@
     </row>
     <row r="122" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2453,22 +2480,22 @@
     </row>
     <row r="126" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2497,22 +2524,22 @@
     </row>
     <row r="130" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>187</v>
+        <v>129</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2541,22 +2568,22 @@
     </row>
     <row r="134" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>188</v>
+        <v>133</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2585,22 +2612,22 @@
     </row>
     <row r="138" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2629,22 +2656,22 @@
     </row>
     <row r="142" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2673,22 +2700,22 @@
     </row>
     <row r="146" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2717,22 +2744,22 @@
     </row>
     <row r="150" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2761,22 +2788,22 @@
     </row>
     <row r="154" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2805,22 +2832,22 @@
     </row>
     <row r="158" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2849,22 +2876,22 @@
     </row>
     <row r="162" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2893,22 +2920,22 @@
     </row>
     <row r="166" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2937,22 +2964,22 @@
     </row>
     <row r="170" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2981,22 +3008,22 @@
     </row>
     <row r="174" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3025,22 +3052,22 @@
     </row>
     <row r="178" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3069,22 +3096,22 @@
     </row>
     <row r="182" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="F182" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3113,22 +3140,22 @@
     </row>
     <row r="186" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="F186" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3157,22 +3184,22 @@
     </row>
     <row r="190" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3201,22 +3228,22 @@
     </row>
     <row r="194" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3245,22 +3272,22 @@
     </row>
     <row r="198" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3291,9 +3318,9 @@
   <mergeCells count="300">
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="C62:C65"/>
-    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A198:A201"/>
     <mergeCell ref="F194:F197"/>
-    <mergeCell ref="A198:A201"/>
     <mergeCell ref="C198:C201"/>
     <mergeCell ref="D122:D125"/>
     <mergeCell ref="C90:C93"/>
@@ -3306,8 +3333,8 @@
     <mergeCell ref="E182:E185"/>
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="F106:F109"/>
+    <mergeCell ref="A190:A193"/>
     <mergeCell ref="F186:F189"/>
-    <mergeCell ref="A190:A193"/>
     <mergeCell ref="C150:C153"/>
     <mergeCell ref="C190:C193"/>
     <mergeCell ref="B114:B117"/>
@@ -3338,8 +3365,8 @@
     <mergeCell ref="B182:B185"/>
     <mergeCell ref="D134:D137"/>
     <mergeCell ref="F134:F137"/>
+    <mergeCell ref="E62:E65"/>
     <mergeCell ref="E22:E25"/>
-    <mergeCell ref="D74:D77"/>
     <mergeCell ref="C194:C197"/>
     <mergeCell ref="C38:C41"/>
     <mergeCell ref="D58:D61"/>
@@ -3364,26 +3391,27 @@
     <mergeCell ref="F158:F161"/>
     <mergeCell ref="B190:B193"/>
     <mergeCell ref="D194:D197"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="B34:B37"/>
     <mergeCell ref="F38:F41"/>
     <mergeCell ref="A42:A45"/>
     <mergeCell ref="B74:B77"/>
     <mergeCell ref="F50:F53"/>
     <mergeCell ref="E162:E165"/>
     <mergeCell ref="D130:D133"/>
-    <mergeCell ref="A14:A17"/>
     <mergeCell ref="A134:A137"/>
     <mergeCell ref="B162:B165"/>
     <mergeCell ref="F130:F133"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="D74:D77"/>
     <mergeCell ref="E134:E137"/>
     <mergeCell ref="D138:D141"/>
     <mergeCell ref="F54:F57"/>
     <mergeCell ref="C158:C161"/>
+    <mergeCell ref="F26:F29"/>
     <mergeCell ref="F154:F157"/>
     <mergeCell ref="A158:A161"/>
+    <mergeCell ref="C118:C121"/>
     <mergeCell ref="D186:D189"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A50:A53"/>
@@ -3404,8 +3432,6 @@
     <mergeCell ref="D146:D149"/>
     <mergeCell ref="E166:E169"/>
     <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="E86:E89"/>
     <mergeCell ref="B198:B201"/>
     <mergeCell ref="D14:D17"/>
     <mergeCell ref="A106:A109"/>
@@ -3504,7 +3530,7 @@
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B158:B161"/>
-    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="E110:E113"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="E2:E5"/>
@@ -3526,37 +3552,6 @@
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="B26:B29"/>
     <mergeCell ref="E50:E53"/>
-    <mergeCell ref="F150:F153"/>
-    <mergeCell ref="E158:E161"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="E74:E77"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="E154:E157"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="F82:F85"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="E130:E133"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="C54:C57"/>
     <mergeCell ref="D198:D201"/>
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A146:A149"/>
@@ -3567,28 +3562,60 @@
     <mergeCell ref="A178:A181"/>
     <mergeCell ref="D126:D129"/>
     <mergeCell ref="C94:C97"/>
-    <mergeCell ref="A74:A77"/>
     <mergeCell ref="F126:F129"/>
     <mergeCell ref="D166:D169"/>
     <mergeCell ref="E94:E97"/>
     <mergeCell ref="E90:E93"/>
     <mergeCell ref="F110:F113"/>
     <mergeCell ref="D150:D153"/>
+    <mergeCell ref="F150:F153"/>
+    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="E154:E157"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="E130:E133"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="C162:C165"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A118:A121"/>
     <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C98:C101"/>
     <mergeCell ref="B66:B69"/>
     <mergeCell ref="C154:C157"/>
-    <mergeCell ref="C98:C101"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="A166:A169"/>
     <mergeCell ref="E102:E105"/>
     <mergeCell ref="B50:B53"/>
     <mergeCell ref="A162:A165"/>
-    <mergeCell ref="C162:C165"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="E18:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SLIIT\3year1sem\ITPM\Test assign\test_automation\IT3040-Assignment1-Singlish-Transliteration-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCE9E8C-8C42-46E6-80AC-A50F9510B102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_BA1814F8542B2BD58D3467F424B7CA55E7DE74B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="210">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -61,12 +61,15 @@
     <t>Neg_0002</t>
   </si>
   <si>
+    <t>ad class ek tiyenwd?</t>
+  </si>
+  <si>
+    <t>අද ක්ලාස් එක තියෙනවද?</t>
+  </si>
+  <si>
     <t>අද class එක තියෙනවද?</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
     <t>Neg_0003</t>
   </si>
   <si>
@@ -136,6 +139,9 @@
     <t>karunkarla report ek ad evnna.</t>
   </si>
   <si>
+    <t>කරුණාකරලා රිපෝර්ට් එක අද එවන්න.</t>
+  </si>
+  <si>
     <t>කරුණාකරලා report එක අද එවන්න.</t>
   </si>
   <si>
@@ -154,13 +160,25 @@
     <t>Neg_0010</t>
   </si>
   <si>
+    <t>ow eke hri.</t>
+  </si>
+  <si>
     <t>ඔව් ඒක හරි.</t>
   </si>
   <si>
+    <t>ඔව් ඒකේ හරි.</t>
+  </si>
+  <si>
     <t>Neg_0011</t>
   </si>
   <si>
-    <t>ටිකක් ටිකක් තේරුණා.</t>
+    <t>mn oyt dn call krnnmm.</t>
+  </si>
+  <si>
+    <t>මං ඔයාට දැන් call කරන්නම්.</t>
+  </si>
+  <si>
+    <t>මන් ඔයාට දැන් call කරන්නම්.</t>
   </si>
   <si>
     <t>Neg_0012</t>
@@ -274,13 +292,25 @@
     <t>Neg_0021</t>
   </si>
   <si>
+    <t>mege email eke update krnn.</t>
+  </si>
+  <si>
     <t>මගේ email එක update කරන්න.</t>
   </si>
   <si>
+    <t>මේ email එකේ update කරන්න.</t>
+  </si>
+  <si>
     <t>Neg_0022</t>
   </si>
   <si>
-    <t>password එක reset කරන්න පුළුවන්ද?</t>
+    <t>password eak reset krn puluwnda?</t>
+  </si>
+  <si>
+    <t>පාස්වර්ඩ් එක reset කරන්න පුළුවන්ද?</t>
+  </si>
+  <si>
+    <t>password එකක් reset කරන්න පුළුවන්ද?</t>
   </si>
   <si>
     <t>Neg_0023</t>
@@ -620,30 +650,6 @@
   </si>
   <si>
     <t>අඩෝ Saturday දවසේ Kandy trip එකට 12 දෙනෙක් යනවා. Rs. 3000ක් අරන් එන්න, location එක WhatsApp group එකට දාන්නම්. ඔයාගේ ID කාඩ් එක අමතක කරන්න එපා. bus එක 6:45AM වලට පිටත් වෙනවා, late උනොත් call එකක් දෙන්න. map link එක email කරන්නම්: trip2026@gmail.කොම් 😎 අපි set එක ආවම attendance list එක Google Sheet එකේ update කරන්න, පස්සේ photos ටික Drive folder එකට upload කරන්න.</t>
-  </si>
-  <si>
-    <t>ad class ek tiyenwd?</t>
-  </si>
-  <si>
-    <t>අද ක්ලාස් එක තියෙනවද?</t>
-  </si>
-  <si>
-    <t>කරුණාකරලා රිපෝර්ට් එක අද එවන්න.</t>
-  </si>
-  <si>
-    <t>ow eke hri.</t>
-  </si>
-  <si>
-    <t>tikakk tikakk terunna.</t>
-  </si>
-  <si>
-    <t>mege email eke update krnn.</t>
-  </si>
-  <si>
-    <t>පාස්වර්ඩ් එක reset කරන්න පුළුවන්ද?</t>
-  </si>
-  <si>
-    <t>password eak reset krn puluwnda?</t>
   </si>
 </sst>
 </file>
@@ -1166,16 +1172,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>201</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1204,19 +1210,19 @@
     </row>
     <row r="10" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>11</v>
@@ -1248,19 +1254,19 @@
     </row>
     <row r="14" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>11</v>
@@ -1292,19 +1298,19 @@
     </row>
     <row r="18" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>11</v>
@@ -1336,19 +1342,19 @@
     </row>
     <row r="22" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>11</v>
@@ -1380,19 +1386,19 @@
     </row>
     <row r="26" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>11</v>
@@ -1424,22 +1430,22 @@
     </row>
     <row r="30" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>202</v>
+        <v>39</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1468,19 +1474,19 @@
     </row>
     <row r="34" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>11</v>
@@ -1512,22 +1518,22 @@
     </row>
     <row r="38" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>203</v>
+        <v>46</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1556,22 +1562,22 @@
     </row>
     <row r="42" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>204</v>
+        <v>50</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1600,19 +1606,19 @@
     </row>
     <row r="46" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>11</v>
@@ -1644,19 +1650,19 @@
     </row>
     <row r="50" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>11</v>
@@ -1688,19 +1694,19 @@
     </row>
     <row r="54" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>11</v>
@@ -1732,19 +1738,19 @@
     </row>
     <row r="58" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>11</v>
@@ -1776,19 +1782,19 @@
     </row>
     <row r="62" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>11</v>
@@ -1820,19 +1826,19 @@
     </row>
     <row r="66" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>11</v>
@@ -1864,19 +1870,19 @@
     </row>
     <row r="70" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>11</v>
@@ -1908,19 +1914,19 @@
     </row>
     <row r="74" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>11</v>
@@ -1952,19 +1958,19 @@
     </row>
     <row r="78" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>11</v>
@@ -1996,22 +2002,22 @@
     </row>
     <row r="82" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>205</v>
+        <v>90</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2040,22 +2046,22 @@
     </row>
     <row r="86" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>207</v>
+        <v>94</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>206</v>
+        <v>95</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2084,19 +2090,19 @@
     </row>
     <row r="90" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>11</v>
@@ -2128,19 +2134,19 @@
     </row>
     <row r="94" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>11</v>
@@ -2172,19 +2178,19 @@
     </row>
     <row r="98" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>11</v>
@@ -2216,19 +2222,19 @@
     </row>
     <row r="102" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>11</v>
@@ -2260,19 +2266,19 @@
     </row>
     <row r="106" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>11</v>
@@ -2304,19 +2310,19 @@
     </row>
     <row r="110" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>11</v>
@@ -2348,19 +2354,19 @@
     </row>
     <row r="114" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>11</v>
@@ -2392,19 +2398,19 @@
     </row>
     <row r="118" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>11</v>
@@ -2436,19 +2442,19 @@
     </row>
     <row r="122" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>11</v>
@@ -2480,19 +2486,19 @@
     </row>
     <row r="126" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>11</v>
@@ -2524,19 +2530,19 @@
     </row>
     <row r="130" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>11</v>
@@ -2568,19 +2574,19 @@
     </row>
     <row r="134" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>11</v>
@@ -2612,19 +2618,19 @@
     </row>
     <row r="138" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>11</v>
@@ -2656,19 +2662,19 @@
     </row>
     <row r="142" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>11</v>
@@ -2700,19 +2706,19 @@
     </row>
     <row r="146" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>11</v>
@@ -2744,19 +2750,19 @@
     </row>
     <row r="150" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>11</v>
@@ -2788,19 +2794,19 @@
     </row>
     <row r="154" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>11</v>
@@ -2832,19 +2838,19 @@
     </row>
     <row r="158" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>11</v>
@@ -2876,19 +2882,19 @@
     </row>
     <row r="162" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>11</v>
@@ -2920,19 +2926,19 @@
     </row>
     <row r="166" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>11</v>
@@ -2964,19 +2970,19 @@
     </row>
     <row r="170" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>11</v>
@@ -3008,19 +3014,19 @@
     </row>
     <row r="174" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>11</v>
@@ -3052,19 +3058,19 @@
     </row>
     <row r="178" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>11</v>
@@ -3096,19 +3102,19 @@
     </row>
     <row r="182" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>11</v>
@@ -3140,19 +3146,19 @@
     </row>
     <row r="186" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>11</v>
@@ -3184,19 +3190,19 @@
     </row>
     <row r="190" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>11</v>
@@ -3228,19 +3234,19 @@
     </row>
     <row r="194" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>11</v>
@@ -3272,19 +3278,19 @@
     </row>
     <row r="198" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>11</v>
@@ -3530,7 +3536,7 @@
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B158:B161"/>
-    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="E154:E157"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="E2:E5"/>
@@ -3572,8 +3578,8 @@
     <mergeCell ref="E158:E161"/>
     <mergeCell ref="B166:B169"/>
     <mergeCell ref="B118:B121"/>
+    <mergeCell ref="E110:E113"/>
     <mergeCell ref="F94:F97"/>
-    <mergeCell ref="E154:E157"/>
     <mergeCell ref="F98:F101"/>
     <mergeCell ref="E130:E133"/>
     <mergeCell ref="F30:F33"/>
